--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260907.xlsx
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,899,013</t>
+          <t>17,522,724</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,522,724</t>
+          <t>7,899,013</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,310,329</t>
+          <t>4,110,343</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4,110,343</t>
+          <t>1,310,329</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
